--- a/data/quizzes/20260324_GloriousBastards.xlsx
+++ b/data/quizzes/20260324_GloriousBastards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/90d082bf22ee60bf/Sonstiges/Pub Quiz/Data/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{82B6AAD6-AEFC-4A09-9A96-DA9F2E6D46DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53EAD2C9-03E6-488F-B15F-52D24AF53EF2}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{82B6AAD6-AEFC-4A09-9A96-DA9F2E6D46DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03AAB767-AA6F-42C4-8908-B8C57F6E9006}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{71070383-C299-4CDA-9D0C-A13D01C1A4EF}"/>
   </bookViews>
@@ -336,6 +336,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -657,6 +661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD51CF4F-7B55-4EE9-8E9D-CA8B67B0F731}">
   <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="28.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -780,7 +787,7 @@
       <c r="K3" s="8">
         <v>4</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="9">
         <v>8</v>
       </c>
       <c r="M3" s="8">
@@ -897,7 +904,7 @@
       <c r="F6" s="8">
         <v>3</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <v>8</v>
       </c>
       <c r="H6" s="8">
@@ -1161,7 +1168,7 @@
       <c r="F12" s="8">
         <v>0</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="9">
         <v>8</v>
       </c>
       <c r="H12" s="8">
@@ -1205,7 +1212,7 @@
       <c r="F13" s="8">
         <v>3</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="9">
         <v>8</v>
       </c>
       <c r="H13" s="8">
@@ -1261,7 +1268,7 @@
       <c r="J14" s="8">
         <v>8</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="9">
         <v>6</v>
       </c>
       <c r="L14" s="8">
@@ -1274,7 +1281,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="28" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <v>14</v>
       </c>
@@ -1305,7 +1312,7 @@
       <c r="J15" s="8">
         <v>6</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="9">
         <v>6</v>
       </c>
       <c r="L15" s="8">
@@ -1387,7 +1394,7 @@
       <c r="H17" s="8">
         <v>4</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="9">
         <v>8</v>
       </c>
       <c r="J17" s="8">
@@ -1428,7 +1435,7 @@
       <c r="G18" s="8">
         <v>4</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="8">
@@ -1481,7 +1488,7 @@
       <c r="J19" s="8">
         <v>6</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="9">
         <v>7</v>
       </c>
       <c r="L19" s="8">
@@ -1548,7 +1555,7 @@
       <c r="C21" s="7">
         <v>10</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="9">
         <v>6</v>
       </c>
       <c r="E21" s="8">
@@ -1745,7 +1752,7 @@
       <c r="J25" s="8">
         <v>6</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="9">
         <v>9</v>
       </c>
       <c r="L25" s="8">
@@ -1890,7 +1897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="28" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="12">
         <v>28</v>
       </c>
@@ -1915,7 +1922,7 @@
       <c r="H29" s="8">
         <v>4</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="9">
         <v>6</v>
       </c>
       <c r="J29" s="8">
@@ -2173,7 +2180,7 @@
       <c r="F35" s="8">
         <v>0</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="9">
         <v>6</v>
       </c>
       <c r="H35" s="8">
@@ -2198,7 +2205,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="42" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
         <v>35</v>
       </c>
@@ -2229,7 +2236,7 @@
       <c r="J36" s="8">
         <v>3</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="9">
         <v>9</v>
       </c>
       <c r="L36" s="8">
@@ -2330,7 +2337,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="12">
         <v>38</v>
       </c>
@@ -2352,7 +2359,7 @@
       <c r="G39" s="8">
         <v>5</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="9">
         <v>6</v>
       </c>
       <c r="I39" s="8">
